--- a/tests/v1/fixtures/office6m/2026-09/bank_statements/TCB_HOLD_USD_2026-08.xlsx
+++ b/tests/v1/fixtures/office6m/2026-09/bank_statements/TCB_HOLD_USD_2026-08.xlsx
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>198829.25</v>
+        <v>202809.25</v>
       </c>
       <c r="E2" t="n">
         <v>650.6799999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
     </row>
     <row r="3">
@@ -640,13 +640,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
     </row>
     <row r="4">
@@ -666,13 +666,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
     </row>
     <row r="5">
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
     </row>
     <row r="6">
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
     </row>
     <row r="7">
@@ -744,13 +744,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
     </row>
     <row r="8">
@@ -770,13 +770,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
     </row>
     <row r="9">
@@ -796,13 +796,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
     </row>
     <row r="10">
@@ -822,13 +822,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
     </row>
     <row r="11">
@@ -848,13 +848,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
     </row>
     <row r="12">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
     </row>
     <row r="13">
@@ -900,13 +900,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
     </row>
     <row r="14">
@@ -926,13 +926,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
     </row>
     <row r="15">
@@ -952,13 +952,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
     </row>
     <row r="16">
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
     </row>
     <row r="17">
@@ -1004,13 +1004,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
     </row>
     <row r="18">
@@ -1030,13 +1030,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
     </row>
     <row r="19">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
     </row>
     <row r="20">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
     </row>
     <row r="21">
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>199479.93</v>
+        <v>203459.93</v>
       </c>
       <c r="E21" t="n">
         <v>-58.48</v>
       </c>
       <c r="F21" t="n">
-        <v>199421.45</v>
+        <v>203401.45</v>
       </c>
     </row>
     <row r="22">
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>199421.45</v>
+        <v>203401.45</v>
       </c>
       <c r="E22" t="n">
         <v>194.82</v>
       </c>
       <c r="F22" t="n">
-        <v>199616.27</v>
+        <v>203596.27</v>
       </c>
     </row>
   </sheetData>
